--- a/test/tcs04_LRU_TextProblem_WT/golden_output.xlsx
+++ b/test/tcs04_LRU_TextProblem_WT/golden_output.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +65,12 @@
       <color rgb="00FF0000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -98,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -129,6 +135,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,16 +508,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.78" customWidth="1" min="1" max="1"/>
-    <col width="27.78" customWidth="1" min="2" max="2"/>
-    <col width="27.78" customWidth="1" min="3" max="3"/>
-    <col width="27.78" customWidth="1" min="4" max="4"/>
-    <col width="27.78" customWidth="1" min="5" max="5"/>
-    <col width="27.78" customWidth="1" min="6" max="6"/>
-    <col width="27.78" customWidth="1" min="7" max="7"/>
+    <col width="34.78" customWidth="1" min="2" max="2"/>
+    <col width="34.78" customWidth="1" min="3" max="3"/>
+    <col width="34.78" customWidth="1" min="4" max="4"/>
+    <col width="34.78" customWidth="1" min="5" max="5"/>
+    <col width="34.78" customWidth="1" min="6" max="6"/>
+    <col width="34.78" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.8" customHeight="1">
@@ -555,37 +564,37 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>20,200
-(V:T, D:F, MCA:T, TS:0, LAT:0)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:0, LAT:0)</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
           <t>0,0
-(V:F, D:F, MCA:F, TS:0, LAT:0)</t>
+(V:F, D:F, VOBI:F, MCA:F, TS:0, LAT:0)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>20,200
-(V:T, D:F, MCA:T, TS:1, LAT:1)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:1, LAT:1)</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
           <t>0,0
-(V:F, D:F, MCA:F, TS:0, LAT:0)</t>
+(V:F, D:F, VOBI:F, MCA:F, TS:0, LAT:0)</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
           <t>0,0
-(V:F, D:F, MCA:F, TS:0, LAT:0)</t>
+(V:F, D:F, VOBI:F, MCA:F, TS:0, LAT:0)</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>0,0
-(V:F, D:F, MCA:F, TS:0, LAT:0)</t>
+(V:F, D:F, VOBI:F, MCA:F, TS:0, LAT:0)</t>
         </is>
       </c>
     </row>
@@ -596,37 +605,37 @@
       <c r="B3" s="5" t="inlineStr">
         <is>
           <t>20,200
-(V:T, D:F, MCA:F, TS:0, LAT:0)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:0, LAT:0)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>21,300
-(V:T, D:F, MCA:T, TS:1, LAT:1)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:1, LAT:1)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
           <t>20,200
-(V:T, D:F, MCA:F, TS:1, LAT:1)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:1, LAT:1)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>21,300
-(V:T, D:F, MCA:T, TS:3, LAT:3)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:3, LAT:3)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>0,0
-(V:F, D:F, MCA:F, TS:0, LAT:0)</t>
+(V:F, D:F, VOBI:F, MCA:F, TS:0, LAT:0)</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>0,0
-(V:F, D:F, MCA:F, TS:0, LAT:0)</t>
+(V:F, D:F, VOBI:F, MCA:F, TS:0, LAT:0)</t>
         </is>
       </c>
     </row>
@@ -637,37 +646,37 @@
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t>22,400
-(V:T, D:F, MCA:T, TS:2, LAT:2)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:2, LAT:2)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>21,300
-(V:T, D:F, MCA:F, TS:1, LAT:1)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:1, LAT:1)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>20,200
-(V:T, D:F, MCA:F, TS:1, LAT:1)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:1, LAT:1)</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>21,300
-(V:T, D:F, MCA:F, TS:3, LAT:3)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:3, LAT:3)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t>22,400
-(V:T, D:F, MCA:T, TS:5, LAT:5)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:5, LAT:5)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>0,0
-(V:F, D:F, MCA:F, TS:0, LAT:0)</t>
+(V:F, D:F, VOBI:F, MCA:F, TS:0, LAT:0)</t>
         </is>
       </c>
     </row>
@@ -678,37 +687,37 @@
       <c r="B5" s="5" t="inlineStr">
         <is>
           <t>22,400
-(V:T, D:F, MCA:F, TS:2, LAT:2)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:2, LAT:2)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>23,500
-(V:T, D:F, MCA:T, TS:3, LAT:3)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:3, LAT:3)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>20,200
-(V:T, D:F, MCA:F, TS:1, LAT:1)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:1, LAT:1)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t>21,300
-(V:T, D:F, MCA:F, TS:3, LAT:3)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:3, LAT:3)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>22,400
-(V:T, D:F, MCA:F, TS:5, LAT:5)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:5, LAT:5)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>23,500
-(V:T, D:F, MCA:T, TS:7, LAT:7)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:7, LAT:7)</t>
         </is>
       </c>
     </row>
@@ -719,37 +728,37 @@
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t>20,201
-(V:T, D:F, MCA:T, TS:4, LAT:4)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:4, LAT:4)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
           <t>23,500
-(V:T, D:F, MCA:F, TS:3, LAT:3)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:3, LAT:3)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>20,201
-(V:T, D:F, MCA:T, TS:9, LAT:9)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:9, LAT:9)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>21,300
-(V:T, D:F, MCA:F, TS:3, LAT:3)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:3, LAT:3)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>22,400
-(V:T, D:F, MCA:F, TS:5, LAT:5)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:5, LAT:5)</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
           <t>23,500
-(V:T, D:F, MCA:F, TS:7, LAT:7)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:7, LAT:7)</t>
         </is>
       </c>
     </row>
@@ -760,37 +769,37 @@
       <c r="B7" s="5" t="inlineStr">
         <is>
           <t>20,201
-(V:T, D:F, MCA:F, TS:4, LAT:4)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:4, LAT:4)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>21,301
-(V:T, D:F, MCA:T, TS:5, LAT:5)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:5, LAT:5)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
           <t>20,201
-(V:T, D:F, MCA:F, TS:9, LAT:9)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:9, LAT:9)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>21,301
-(V:T, D:F, MCA:T, TS:11, LAT:11)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:11, LAT:11)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>22,400
-(V:T, D:F, MCA:F, TS:5, LAT:5)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:5, LAT:5)</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
           <t>23,500
-(V:T, D:F, MCA:F, TS:7, LAT:7)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:7, LAT:7)</t>
         </is>
       </c>
     </row>
@@ -801,37 +810,37 @@
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>22,400
-(V:T, D:F, MCA:T, TS:6, LAT:6)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:6, LAT:6)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>21,301
-(V:T, D:F, MCA:F, TS:5, LAT:5)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:5, LAT:5)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>20,201
-(V:T, D:F, MCA:F, TS:9, LAT:9)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:9, LAT:9)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>21,301
-(V:T, D:F, MCA:F, TS:11, LAT:11)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:11, LAT:11)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>22,400
-(V:T, D:F, MCA:F, TS:5, LAT:12)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:5, LAT:12)</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>23,500
-(V:T, D:F, MCA:F, TS:7, LAT:7)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:7, LAT:7)</t>
         </is>
       </c>
     </row>
@@ -842,37 +851,37 @@
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>22,400
-(V:T, D:F, MCA:F, TS:6, LAT:6)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:6, LAT:6)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
           <t>23,500
-(V:T, D:F, MCA:T, TS:7, LAT:7)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:7, LAT:7)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>20,201
-(V:T, D:F, MCA:F, TS:9, LAT:9)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:9, LAT:9)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>21,301
-(V:T, D:F, MCA:F, TS:11, LAT:11)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:11, LAT:11)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>22,400
-(V:T, D:F, MCA:F, TS:5, LAT:12)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:5, LAT:12)</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
           <t>23,500
-(V:T, D:F, MCA:F, TS:7, LAT:13)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:7, LAT:13)</t>
         </is>
       </c>
     </row>
@@ -883,37 +892,37 @@
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>22,401
-(V:T, D:F, MCA:T, TS:8, LAT:8)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:8, LAT:8)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
           <t>23,500
-(V:T, D:F, MCA:F, TS:7, LAT:7)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:7, LAT:7)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
           <t>20,201
-(V:T, D:F, MCA:F, TS:9, LAT:9)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:9, LAT:9)</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>21,301
-(V:T, D:F, MCA:F, TS:11, LAT:11)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:11, LAT:11)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>22,401
-(V:T, D:F, MCA:T, TS:14, LAT:14)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:14, LAT:14)</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
           <t>23,500
-(V:T, D:F, MCA:F, TS:7, LAT:13)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:7, LAT:13)</t>
         </is>
       </c>
     </row>
@@ -924,37 +933,37 @@
       <c r="B11" s="5" t="inlineStr">
         <is>
           <t>22,401
-(V:T, D:F, MCA:F, TS:8, LAT:8)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:8, LAT:8)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
           <t>23,501
-(V:T, D:F, MCA:T, TS:9, LAT:9)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:9, LAT:9)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
           <t>20,201
-(V:T, D:F, MCA:F, TS:9, LAT:9)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:9, LAT:9)</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
           <t>21,301
-(V:T, D:F, MCA:F, TS:11, LAT:11)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:11, LAT:11)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>22,401
-(V:T, D:F, MCA:F, TS:14, LAT:14)</t>
+(V:T, D:F, VOBI:F, MCA:F, TS:14, LAT:14)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>23,501
-(V:T, D:F, MCA:T, TS:15, LAT:15)</t>
+(V:T, D:F, VOBI:F, MCA:T, TS:15, LAT:15)</t>
         </is>
       </c>
     </row>
@@ -1020,6 +1029,18 @@
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Victim Of Back Invalidation (VOBI:T), possibly subsequently populated with valid data</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Unused entry available for use (V:F)</t>
         </is>
